--- a/서버정보/20260811_리소스배포_랜딩.xlsx
+++ b/서버정보/20260811_리소스배포_랜딩.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0955E6FD-80BA-4906-A7DC-E02F6D42BE12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47917B23-C739-47E6-AA5A-6526EDBF6D0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VM" sheetId="1" r:id="rId1"/>
@@ -1658,7 +1658,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2014" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2118" uniqueCount="358">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2996,6 +2996,30 @@
   </si>
   <si>
     <t>TEMP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>az-grayzone-host1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>az-grayzone-host2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>az-grayzone-host3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>az-grayzone-host4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.155.161.198</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.155.161.199</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3169,7 +3193,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="24">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -3474,13 +3498,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="110">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3797,6 +3832,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4993,8 +5034,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표1" displayName="표1" ref="B1:AF15" totalsRowShown="0" headerRowDxfId="32" dataDxfId="31">
-  <autoFilter ref="B1:AF15" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표1" displayName="표1" ref="B1:AF19" totalsRowShown="0" headerRowDxfId="32" dataDxfId="31">
+  <autoFilter ref="B1:AF19" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="31">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Stage" dataDxfId="30"/>
     <tableColumn id="2" xr3:uid="{DD2076C4-D866-4329-BEA8-1D816DAF3627}" name="Role" dataDxfId="29">
@@ -5338,7 +5379,7 @@
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:AF15"/>
+  <dimension ref="A1:AF19"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.25" customWidth="1"/>
@@ -5957,7 +5998,7 @@
         <v>288</v>
       </c>
       <c r="O7" s="98" t="str">
-        <f>SUBSTITUTE(F7,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" ref="O7:O15" si="4">SUBSTITUTE(F7,"hazr-","")&amp;"-osdisk"</f>
         <v>l-sec-virsol01-osdisk</v>
       </c>
       <c r="P7" s="99">
@@ -5970,7 +6011,7 @@
       <c r="S7" s="88"/>
       <c r="T7" s="88"/>
       <c r="U7" s="88" t="str">
-        <f>SUBSTITUTE(F7,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" ref="U7:U15" si="5">SUBSTITUTE(F7,"hazr-","")&amp;"-nic"</f>
         <v>l-sec-virsol01-nic</v>
       </c>
       <c r="V7" s="88" t="b">
@@ -6046,7 +6087,7 @@
         <v>293</v>
       </c>
       <c r="O8" s="98" t="str">
-        <f>SUBSTITUTE(F8,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="4"/>
         <v>l-sec-wbdsol01-osdisk</v>
       </c>
       <c r="P8" s="99">
@@ -6059,7 +6100,7 @@
       <c r="S8" s="88"/>
       <c r="T8" s="88"/>
       <c r="U8" s="88" t="str">
-        <f>SUBSTITUTE(F8,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="5"/>
         <v>l-sec-wbdsol01-nic</v>
       </c>
       <c r="V8" s="88" t="b">
@@ -6135,7 +6176,7 @@
         <v>297</v>
       </c>
       <c r="O9" s="98" t="str">
-        <f>SUBSTITUTE(F9,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="4"/>
         <v>l-com-scmsol01-osdisk</v>
       </c>
       <c r="P9" s="99">
@@ -6148,7 +6189,7 @@
       <c r="S9" s="88"/>
       <c r="T9" s="88"/>
       <c r="U9" s="88" t="str">
-        <f>SUBSTITUTE(F9,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="5"/>
         <v>l-com-scmsol01-nic</v>
       </c>
       <c r="V9" s="88" t="b">
@@ -6224,7 +6265,7 @@
         <v>330</v>
       </c>
       <c r="O10" s="98" t="str">
-        <f>SUBSTITUTE(F10,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="4"/>
         <v>l-if-hipsproxy01-osdisk</v>
       </c>
       <c r="P10" s="99">
@@ -6237,7 +6278,7 @@
       <c r="S10" s="88"/>
       <c r="T10" s="88"/>
       <c r="U10" s="88" t="str">
-        <f>SUBSTITUTE(F10,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="5"/>
         <v>l-if-hipsproxy01-nic</v>
       </c>
       <c r="V10" s="88" t="b">
@@ -6313,7 +6354,7 @@
         <v>336</v>
       </c>
       <c r="O11" s="98" t="str">
-        <f>SUBSTITUTE(F11,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="4"/>
         <v>l-if-sastsol01-osdisk</v>
       </c>
       <c r="P11" s="99">
@@ -6326,7 +6367,7 @@
       <c r="S11" s="88"/>
       <c r="T11" s="88"/>
       <c r="U11" s="88" t="str">
-        <f>SUBSTITUTE(F11,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="5"/>
         <v>l-if-sastsol01-nic</v>
       </c>
       <c r="V11" s="88" t="b">
@@ -6363,7 +6404,7 @@
       <c r="B12" s="88" t="s">
         <v>321</v>
       </c>
-      <c r="C12" s="106" t="s">
+      <c r="C12" s="88" t="s">
         <v>340</v>
       </c>
       <c r="D12" s="88" t="s">
@@ -6399,8 +6440,8 @@
       <c r="N12" s="97" t="s">
         <v>349</v>
       </c>
-      <c r="O12" s="107" t="str">
-        <f>SUBSTITUTE(F12,"hazr-","")&amp;"-osdisk"</f>
+      <c r="O12" s="98" t="str">
+        <f t="shared" si="4"/>
         <v>az-erdirect-host1-osdisk</v>
       </c>
       <c r="P12" s="99">
@@ -6409,11 +6450,11 @@
       <c r="Q12" s="100" t="s">
         <v>121</v>
       </c>
-      <c r="R12" s="106"/>
+      <c r="R12" s="88"/>
       <c r="S12" s="88"/>
-      <c r="T12" s="106"/>
-      <c r="U12" s="106" t="str">
-        <f>SUBSTITUTE(F12,"hazr-","")&amp;"-nic"</f>
+      <c r="T12" s="88"/>
+      <c r="U12" s="88" t="str">
+        <f t="shared" si="5"/>
         <v>az-erdirect-host1-nic</v>
       </c>
       <c r="V12" s="88" t="b">
@@ -6450,7 +6491,7 @@
       <c r="B13" s="88" t="s">
         <v>321</v>
       </c>
-      <c r="C13" s="106" t="s">
+      <c r="C13" s="88" t="s">
         <v>340</v>
       </c>
       <c r="D13" s="88" t="s">
@@ -6486,8 +6527,8 @@
       <c r="N13" s="97" t="s">
         <v>349</v>
       </c>
-      <c r="O13" s="107" t="str">
-        <f>SUBSTITUTE(F13,"hazr-","")&amp;"-osdisk"</f>
+      <c r="O13" s="98" t="str">
+        <f t="shared" si="4"/>
         <v>az-erdirect-host2-osdisk</v>
       </c>
       <c r="P13" s="99">
@@ -6496,11 +6537,11 @@
       <c r="Q13" s="100" t="s">
         <v>121</v>
       </c>
-      <c r="R13" s="106"/>
+      <c r="R13" s="88"/>
       <c r="S13" s="88"/>
-      <c r="T13" s="106"/>
-      <c r="U13" s="106" t="str">
-        <f>SUBSTITUTE(F13,"hazr-","")&amp;"-nic"</f>
+      <c r="T13" s="88"/>
+      <c r="U13" s="88" t="str">
+        <f t="shared" si="5"/>
         <v>az-erdirect-host2-nic</v>
       </c>
       <c r="V13" s="88" t="b">
@@ -6537,7 +6578,7 @@
       <c r="B14" s="88" t="s">
         <v>321</v>
       </c>
-      <c r="C14" s="106" t="s">
+      <c r="C14" s="88" t="s">
         <v>340</v>
       </c>
       <c r="D14" s="88" t="s">
@@ -6573,8 +6614,8 @@
       <c r="N14" s="97" t="s">
         <v>349</v>
       </c>
-      <c r="O14" s="107" t="str">
-        <f>SUBSTITUTE(F14,"hazr-","")&amp;"-osdisk"</f>
+      <c r="O14" s="98" t="str">
+        <f t="shared" si="4"/>
         <v>az-erdirect-host3-osdisk</v>
       </c>
       <c r="P14" s="99">
@@ -6583,11 +6624,11 @@
       <c r="Q14" s="100" t="s">
         <v>121</v>
       </c>
-      <c r="R14" s="106"/>
+      <c r="R14" s="88"/>
       <c r="S14" s="88"/>
-      <c r="T14" s="106"/>
-      <c r="U14" s="106" t="str">
-        <f>SUBSTITUTE(F14,"hazr-","")&amp;"-nic"</f>
+      <c r="T14" s="88"/>
+      <c r="U14" s="88" t="str">
+        <f t="shared" si="5"/>
         <v>az-erdirect-host3-nic</v>
       </c>
       <c r="V14" s="88" t="b">
@@ -6624,7 +6665,7 @@
       <c r="B15" s="88" t="s">
         <v>321</v>
       </c>
-      <c r="C15" s="106" t="s">
+      <c r="C15" s="88" t="s">
         <v>340</v>
       </c>
       <c r="D15" s="88" t="s">
@@ -6660,8 +6701,8 @@
       <c r="N15" s="97" t="s">
         <v>349</v>
       </c>
-      <c r="O15" s="107" t="str">
-        <f>SUBSTITUTE(F15,"hazr-","")&amp;"-osdisk"</f>
+      <c r="O15" s="98" t="str">
+        <f t="shared" si="4"/>
         <v>az-erdirect-host4-osdisk</v>
       </c>
       <c r="P15" s="99">
@@ -6670,11 +6711,11 @@
       <c r="Q15" s="100" t="s">
         <v>121</v>
       </c>
-      <c r="R15" s="106"/>
+      <c r="R15" s="88"/>
       <c r="S15" s="88"/>
-      <c r="T15" s="106"/>
-      <c r="U15" s="106" t="str">
-        <f>SUBSTITUTE(F15,"hazr-","")&amp;"-nic"</f>
+      <c r="T15" s="88"/>
+      <c r="U15" s="88" t="str">
+        <f t="shared" si="5"/>
         <v>az-erdirect-host4-nic</v>
       </c>
       <c r="V15" s="88" t="b">
@@ -6706,6 +6747,354 @@
       </c>
       <c r="AE15" s="88"/>
       <c r="AF15" s="88"/>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B16" s="69" t="s">
+        <v>321</v>
+      </c>
+      <c r="C16" s="106" t="s">
+        <v>340</v>
+      </c>
+      <c r="D16" s="88" t="s">
+        <v>145</v>
+      </c>
+      <c r="E16" s="88" t="s">
+        <v>24</v>
+      </c>
+      <c r="F16" s="69" t="s">
+        <v>352</v>
+      </c>
+      <c r="G16" s="69" t="s">
+        <v>345</v>
+      </c>
+      <c r="H16" s="88" t="s">
+        <v>329</v>
+      </c>
+      <c r="I16" s="88">
+        <v>2</v>
+      </c>
+      <c r="J16" s="88">
+        <v>8</v>
+      </c>
+      <c r="K16" s="88" t="s">
+        <v>122</v>
+      </c>
+      <c r="L16" s="96" t="s">
+        <v>120</v>
+      </c>
+      <c r="M16" s="88" t="s">
+        <v>292</v>
+      </c>
+      <c r="N16" s="97" t="s">
+        <v>349</v>
+      </c>
+      <c r="O16" s="107" t="str">
+        <f t="shared" ref="O16:O19" si="6">SUBSTITUTE(F16,"hazr-","")&amp;"-osdisk"</f>
+        <v>az-grayzone-host1-osdisk</v>
+      </c>
+      <c r="P16" s="99">
+        <v>64</v>
+      </c>
+      <c r="Q16" s="100" t="s">
+        <v>121</v>
+      </c>
+      <c r="R16" s="106"/>
+      <c r="S16" s="69"/>
+      <c r="T16" s="106"/>
+      <c r="U16" s="106" t="str">
+        <f t="shared" ref="U16:U19" si="7">SUBSTITUTE(F16,"hazr-","")&amp;"-nic"</f>
+        <v>az-grayzone-host1-nic</v>
+      </c>
+      <c r="V16" s="88" t="b">
+        <v>1</v>
+      </c>
+      <c r="W16" s="88" t="b">
+        <v>1</v>
+      </c>
+      <c r="X16" s="88" t="s">
+        <v>145</v>
+      </c>
+      <c r="Y16" s="69" t="s">
+        <v>138</v>
+      </c>
+      <c r="Z16" s="69" t="s">
+        <v>290</v>
+      </c>
+      <c r="AA16" s="88" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB16" s="88" t="s">
+        <v>145</v>
+      </c>
+      <c r="AC16" s="88" t="s">
+        <v>146</v>
+      </c>
+      <c r="AD16" s="99">
+        <v>1</v>
+      </c>
+      <c r="AE16" s="69"/>
+      <c r="AF16" s="69"/>
+    </row>
+    <row r="17" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B17" s="69" t="s">
+        <v>321</v>
+      </c>
+      <c r="C17" s="106" t="s">
+        <v>340</v>
+      </c>
+      <c r="D17" s="88" t="s">
+        <v>145</v>
+      </c>
+      <c r="E17" s="88" t="s">
+        <v>24</v>
+      </c>
+      <c r="F17" s="69" t="s">
+        <v>353</v>
+      </c>
+      <c r="G17" s="69" t="s">
+        <v>346</v>
+      </c>
+      <c r="H17" s="88" t="s">
+        <v>329</v>
+      </c>
+      <c r="I17" s="88">
+        <v>2</v>
+      </c>
+      <c r="J17" s="88">
+        <v>8</v>
+      </c>
+      <c r="K17" s="88" t="s">
+        <v>122</v>
+      </c>
+      <c r="L17" s="96" t="s">
+        <v>120</v>
+      </c>
+      <c r="M17" s="88" t="s">
+        <v>292</v>
+      </c>
+      <c r="N17" s="97" t="s">
+        <v>349</v>
+      </c>
+      <c r="O17" s="107" t="str">
+        <f t="shared" si="6"/>
+        <v>az-grayzone-host2-osdisk</v>
+      </c>
+      <c r="P17" s="99">
+        <v>64</v>
+      </c>
+      <c r="Q17" s="100" t="s">
+        <v>121</v>
+      </c>
+      <c r="R17" s="106"/>
+      <c r="S17" s="69"/>
+      <c r="T17" s="106"/>
+      <c r="U17" s="106" t="str">
+        <f t="shared" si="7"/>
+        <v>az-grayzone-host2-nic</v>
+      </c>
+      <c r="V17" s="88" t="b">
+        <v>1</v>
+      </c>
+      <c r="W17" s="88" t="b">
+        <v>1</v>
+      </c>
+      <c r="X17" s="88" t="s">
+        <v>145</v>
+      </c>
+      <c r="Y17" s="88" t="s">
+        <v>138</v>
+      </c>
+      <c r="Z17" s="88" t="s">
+        <v>290</v>
+      </c>
+      <c r="AA17" s="88" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB17" s="88" t="s">
+        <v>145</v>
+      </c>
+      <c r="AC17" s="88" t="s">
+        <v>146</v>
+      </c>
+      <c r="AD17" s="99">
+        <v>1</v>
+      </c>
+      <c r="AE17" s="69"/>
+      <c r="AF17" s="69"/>
+    </row>
+    <row r="18" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B18" s="69" t="s">
+        <v>321</v>
+      </c>
+      <c r="C18" s="106" t="s">
+        <v>340</v>
+      </c>
+      <c r="D18" s="88" t="s">
+        <v>145</v>
+      </c>
+      <c r="E18" s="88" t="s">
+        <v>24</v>
+      </c>
+      <c r="F18" s="69" t="s">
+        <v>354</v>
+      </c>
+      <c r="G18" s="69" t="s">
+        <v>356</v>
+      </c>
+      <c r="H18" s="88" t="s">
+        <v>329</v>
+      </c>
+      <c r="I18" s="88">
+        <v>2</v>
+      </c>
+      <c r="J18" s="88">
+        <v>8</v>
+      </c>
+      <c r="K18" s="88" t="s">
+        <v>122</v>
+      </c>
+      <c r="L18" s="96" t="s">
+        <v>120</v>
+      </c>
+      <c r="M18" s="88" t="s">
+        <v>292</v>
+      </c>
+      <c r="N18" s="97" t="s">
+        <v>349</v>
+      </c>
+      <c r="O18" s="107" t="str">
+        <f t="shared" si="6"/>
+        <v>az-grayzone-host3-osdisk</v>
+      </c>
+      <c r="P18" s="99">
+        <v>64</v>
+      </c>
+      <c r="Q18" s="100" t="s">
+        <v>121</v>
+      </c>
+      <c r="R18" s="106"/>
+      <c r="S18" s="69"/>
+      <c r="T18" s="106"/>
+      <c r="U18" s="106" t="str">
+        <f t="shared" si="7"/>
+        <v>az-grayzone-host3-nic</v>
+      </c>
+      <c r="V18" s="88" t="b">
+        <v>1</v>
+      </c>
+      <c r="W18" s="88" t="b">
+        <v>1</v>
+      </c>
+      <c r="X18" s="88" t="s">
+        <v>145</v>
+      </c>
+      <c r="Y18" s="69" t="s">
+        <v>138</v>
+      </c>
+      <c r="Z18" s="69" t="s">
+        <v>290</v>
+      </c>
+      <c r="AA18" s="88" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB18" s="88" t="s">
+        <v>145</v>
+      </c>
+      <c r="AC18" s="88" t="s">
+        <v>146</v>
+      </c>
+      <c r="AD18" s="99">
+        <v>1</v>
+      </c>
+      <c r="AE18" s="69"/>
+      <c r="AF18" s="69"/>
+    </row>
+    <row r="19" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B19" s="88" t="s">
+        <v>321</v>
+      </c>
+      <c r="C19" s="108" t="s">
+        <v>340</v>
+      </c>
+      <c r="D19" s="88" t="s">
+        <v>145</v>
+      </c>
+      <c r="E19" s="88" t="s">
+        <v>24</v>
+      </c>
+      <c r="F19" s="88" t="s">
+        <v>355</v>
+      </c>
+      <c r="G19" s="88" t="s">
+        <v>357</v>
+      </c>
+      <c r="H19" s="88" t="s">
+        <v>329</v>
+      </c>
+      <c r="I19" s="88">
+        <v>2</v>
+      </c>
+      <c r="J19" s="88">
+        <v>8</v>
+      </c>
+      <c r="K19" s="88" t="s">
+        <v>122</v>
+      </c>
+      <c r="L19" s="96" t="s">
+        <v>120</v>
+      </c>
+      <c r="M19" s="88" t="s">
+        <v>292</v>
+      </c>
+      <c r="N19" s="97" t="s">
+        <v>349</v>
+      </c>
+      <c r="O19" s="109" t="str">
+        <f t="shared" si="6"/>
+        <v>az-grayzone-host4-osdisk</v>
+      </c>
+      <c r="P19" s="99">
+        <v>64</v>
+      </c>
+      <c r="Q19" s="100" t="s">
+        <v>121</v>
+      </c>
+      <c r="R19" s="108"/>
+      <c r="S19" s="88"/>
+      <c r="T19" s="108"/>
+      <c r="U19" s="108" t="str">
+        <f t="shared" si="7"/>
+        <v>az-grayzone-host4-nic</v>
+      </c>
+      <c r="V19" s="88" t="b">
+        <v>1</v>
+      </c>
+      <c r="W19" s="88" t="b">
+        <v>1</v>
+      </c>
+      <c r="X19" s="88" t="s">
+        <v>145</v>
+      </c>
+      <c r="Y19" s="88" t="s">
+        <v>138</v>
+      </c>
+      <c r="Z19" s="88" t="s">
+        <v>290</v>
+      </c>
+      <c r="AA19" s="88" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB19" s="88" t="s">
+        <v>145</v>
+      </c>
+      <c r="AC19" s="88" t="s">
+        <v>146</v>
+      </c>
+      <c r="AD19" s="99">
+        <v>1</v>
+      </c>
+      <c r="AE19" s="88"/>
+      <c r="AF19" s="88"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -8528,7 +8917,7 @@
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.5" customWidth="1"/>
@@ -8992,7 +9381,7 @@
         <v>145</v>
       </c>
       <c r="E12" s="73" t="str">
-        <f t="shared" ref="E12:E15" si="8">SUBSTITUTE(I12,"hazr-","")&amp;"-nsg"</f>
+        <f t="shared" ref="E12:E19" si="8">SUBSTITUTE(I12,"hazr-","")&amp;"-nsg"</f>
         <v>az-erdirect-host1-nsg</v>
       </c>
       <c r="F12" s="73" t="s">
@@ -9049,7 +9438,7 @@
         <v>145</v>
       </c>
       <c r="K13" s="75" t="str">
-        <f t="shared" ref="K13:K15" si="9">SUBSTITUTE(I13,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" ref="K13:K16" si="9">SUBSTITUTE(I13,"hazr-","")&amp;"-nic"</f>
         <v>az-erdirect-host2-nic</v>
       </c>
       <c r="L13" s="75" t="s">
@@ -9132,6 +9521,158 @@
         <v>141</v>
       </c>
       <c r="M15" s="75"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B16" s="73" t="s">
+        <v>321</v>
+      </c>
+      <c r="C16" s="73" t="s">
+        <v>340</v>
+      </c>
+      <c r="D16" s="73" t="s">
+        <v>145</v>
+      </c>
+      <c r="E16" s="73" t="str">
+        <f t="shared" si="8"/>
+        <v>az-grayzone-host1-nsg</v>
+      </c>
+      <c r="F16" s="73" t="s">
+        <v>145</v>
+      </c>
+      <c r="G16" s="73" t="s">
+        <v>138</v>
+      </c>
+      <c r="H16" s="73" t="s">
+        <v>290</v>
+      </c>
+      <c r="I16" s="68" t="s">
+        <v>352</v>
+      </c>
+      <c r="J16" s="73" t="s">
+        <v>145</v>
+      </c>
+      <c r="K16" s="73" t="str">
+        <f t="shared" si="9"/>
+        <v>az-grayzone-host1-nic</v>
+      </c>
+      <c r="L16" s="73" t="s">
+        <v>141</v>
+      </c>
+      <c r="M16" s="73"/>
+    </row>
+    <row r="17" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B17" s="75" t="s">
+        <v>321</v>
+      </c>
+      <c r="C17" s="75" t="s">
+        <v>340</v>
+      </c>
+      <c r="D17" s="75" t="s">
+        <v>145</v>
+      </c>
+      <c r="E17" s="75" t="str">
+        <f t="shared" si="8"/>
+        <v>az-grayzone-host2-nsg</v>
+      </c>
+      <c r="F17" s="75" t="s">
+        <v>145</v>
+      </c>
+      <c r="G17" s="75" t="s">
+        <v>138</v>
+      </c>
+      <c r="H17" s="75" t="s">
+        <v>290</v>
+      </c>
+      <c r="I17" s="69" t="s">
+        <v>353</v>
+      </c>
+      <c r="J17" s="75" t="s">
+        <v>145</v>
+      </c>
+      <c r="K17" s="75" t="str">
+        <f t="shared" ref="K17:K19" si="10">SUBSTITUTE(I17,"hazr-","")&amp;"-nic"</f>
+        <v>az-grayzone-host2-nic</v>
+      </c>
+      <c r="L17" s="75" t="s">
+        <v>141</v>
+      </c>
+      <c r="M17" s="75"/>
+    </row>
+    <row r="18" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B18" s="73" t="s">
+        <v>321</v>
+      </c>
+      <c r="C18" s="73" t="s">
+        <v>340</v>
+      </c>
+      <c r="D18" s="73" t="s">
+        <v>145</v>
+      </c>
+      <c r="E18" s="73" t="str">
+        <f t="shared" si="8"/>
+        <v>az-grayzone-host3-nsg</v>
+      </c>
+      <c r="F18" s="73" t="s">
+        <v>145</v>
+      </c>
+      <c r="G18" s="73" t="s">
+        <v>138</v>
+      </c>
+      <c r="H18" s="73" t="s">
+        <v>290</v>
+      </c>
+      <c r="I18" s="68" t="s">
+        <v>354</v>
+      </c>
+      <c r="J18" s="73" t="s">
+        <v>145</v>
+      </c>
+      <c r="K18" s="73" t="str">
+        <f t="shared" si="10"/>
+        <v>az-grayzone-host3-nic</v>
+      </c>
+      <c r="L18" s="73" t="s">
+        <v>141</v>
+      </c>
+      <c r="M18" s="73"/>
+    </row>
+    <row r="19" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B19" s="75" t="s">
+        <v>321</v>
+      </c>
+      <c r="C19" s="75" t="s">
+        <v>340</v>
+      </c>
+      <c r="D19" s="75" t="s">
+        <v>145</v>
+      </c>
+      <c r="E19" s="75" t="str">
+        <f t="shared" si="8"/>
+        <v>az-grayzone-host4-nsg</v>
+      </c>
+      <c r="F19" s="75" t="s">
+        <v>145</v>
+      </c>
+      <c r="G19" s="75" t="s">
+        <v>138</v>
+      </c>
+      <c r="H19" s="75" t="s">
+        <v>290</v>
+      </c>
+      <c r="I19" s="101" t="s">
+        <v>355</v>
+      </c>
+      <c r="J19" s="75" t="s">
+        <v>145</v>
+      </c>
+      <c r="K19" s="75" t="str">
+        <f t="shared" si="10"/>
+        <v>az-grayzone-host4-nic</v>
+      </c>
+      <c r="L19" s="75" t="s">
+        <v>141</v>
+      </c>
+      <c r="M19" s="75"/>
     </row>
   </sheetData>
   <autoFilter ref="B1:M9" xr:uid="{BAB1F184-7BFC-47CB-AC71-63C76B7E3D12}"/>
@@ -17350,9 +17891,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -17500,26 +18044,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -17543,9 +18076,17 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/서버정보/20260811_리소스배포_랜딩.xlsx
+++ b/서버정보/20260811_리소스배포_랜딩.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47917B23-C739-47E6-AA5A-6526EDBF6D0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37B2855E-A9FD-4D3C-B02E-5350AC9100C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1658,7 +1658,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2118" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2118" uniqueCount="360">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3015,11 +3015,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>10.155.161.198</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10.155.161.199</t>
+    <t>10.155.161.156</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.155.161.157</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.155.161.158</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.155.161.159</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3515,7 +3523,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="110">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3834,16 +3842,7 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -6752,7 +6751,7 @@
       <c r="B16" s="69" t="s">
         <v>321</v>
       </c>
-      <c r="C16" s="106" t="s">
+      <c r="C16" s="69" t="s">
         <v>340</v>
       </c>
       <c r="D16" s="88" t="s">
@@ -6765,7 +6764,7 @@
         <v>352</v>
       </c>
       <c r="G16" s="69" t="s">
-        <v>345</v>
+        <v>356</v>
       </c>
       <c r="H16" s="88" t="s">
         <v>329</v>
@@ -6788,7 +6787,7 @@
       <c r="N16" s="97" t="s">
         <v>349</v>
       </c>
-      <c r="O16" s="107" t="str">
+      <c r="O16" s="106" t="str">
         <f t="shared" ref="O16:O19" si="6">SUBSTITUTE(F16,"hazr-","")&amp;"-osdisk"</f>
         <v>az-grayzone-host1-osdisk</v>
       </c>
@@ -6798,10 +6797,10 @@
       <c r="Q16" s="100" t="s">
         <v>121</v>
       </c>
-      <c r="R16" s="106"/>
+      <c r="R16" s="69"/>
       <c r="S16" s="69"/>
-      <c r="T16" s="106"/>
-      <c r="U16" s="106" t="str">
+      <c r="T16" s="69"/>
+      <c r="U16" s="69" t="str">
         <f t="shared" ref="U16:U19" si="7">SUBSTITUTE(F16,"hazr-","")&amp;"-nic"</f>
         <v>az-grayzone-host1-nic</v>
       </c>
@@ -6839,7 +6838,7 @@
       <c r="B17" s="69" t="s">
         <v>321</v>
       </c>
-      <c r="C17" s="106" t="s">
+      <c r="C17" s="69" t="s">
         <v>340</v>
       </c>
       <c r="D17" s="88" t="s">
@@ -6852,7 +6851,7 @@
         <v>353</v>
       </c>
       <c r="G17" s="69" t="s">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="H17" s="88" t="s">
         <v>329</v>
@@ -6875,7 +6874,7 @@
       <c r="N17" s="97" t="s">
         <v>349</v>
       </c>
-      <c r="O17" s="107" t="str">
+      <c r="O17" s="106" t="str">
         <f t="shared" si="6"/>
         <v>az-grayzone-host2-osdisk</v>
       </c>
@@ -6885,10 +6884,10 @@
       <c r="Q17" s="100" t="s">
         <v>121</v>
       </c>
-      <c r="R17" s="106"/>
+      <c r="R17" s="69"/>
       <c r="S17" s="69"/>
-      <c r="T17" s="106"/>
-      <c r="U17" s="106" t="str">
+      <c r="T17" s="69"/>
+      <c r="U17" s="69" t="str">
         <f t="shared" si="7"/>
         <v>az-grayzone-host2-nic</v>
       </c>
@@ -6926,7 +6925,7 @@
       <c r="B18" s="69" t="s">
         <v>321</v>
       </c>
-      <c r="C18" s="106" t="s">
+      <c r="C18" s="69" t="s">
         <v>340</v>
       </c>
       <c r="D18" s="88" t="s">
@@ -6939,7 +6938,7 @@
         <v>354</v>
       </c>
       <c r="G18" s="69" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="H18" s="88" t="s">
         <v>329</v>
@@ -6962,7 +6961,7 @@
       <c r="N18" s="97" t="s">
         <v>349</v>
       </c>
-      <c r="O18" s="107" t="str">
+      <c r="O18" s="106" t="str">
         <f t="shared" si="6"/>
         <v>az-grayzone-host3-osdisk</v>
       </c>
@@ -6972,10 +6971,10 @@
       <c r="Q18" s="100" t="s">
         <v>121</v>
       </c>
-      <c r="R18" s="106"/>
+      <c r="R18" s="69"/>
       <c r="S18" s="69"/>
-      <c r="T18" s="106"/>
-      <c r="U18" s="106" t="str">
+      <c r="T18" s="69"/>
+      <c r="U18" s="69" t="str">
         <f t="shared" si="7"/>
         <v>az-grayzone-host3-nic</v>
       </c>
@@ -7013,7 +7012,7 @@
       <c r="B19" s="88" t="s">
         <v>321</v>
       </c>
-      <c r="C19" s="108" t="s">
+      <c r="C19" s="88" t="s">
         <v>340</v>
       </c>
       <c r="D19" s="88" t="s">
@@ -7026,7 +7025,7 @@
         <v>355</v>
       </c>
       <c r="G19" s="88" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="H19" s="88" t="s">
         <v>329</v>
@@ -7049,7 +7048,7 @@
       <c r="N19" s="97" t="s">
         <v>349</v>
       </c>
-      <c r="O19" s="109" t="str">
+      <c r="O19" s="98" t="str">
         <f t="shared" si="6"/>
         <v>az-grayzone-host4-osdisk</v>
       </c>
@@ -7059,10 +7058,10 @@
       <c r="Q19" s="100" t="s">
         <v>121</v>
       </c>
-      <c r="R19" s="108"/>
+      <c r="R19" s="88"/>
       <c r="S19" s="88"/>
-      <c r="T19" s="108"/>
-      <c r="U19" s="108" t="str">
+      <c r="T19" s="88"/>
+      <c r="U19" s="88" t="str">
         <f t="shared" si="7"/>
         <v>az-grayzone-host4-nic</v>
       </c>
@@ -17891,12 +17890,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -18044,15 +18040,26 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -18076,17 +18083,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/서버정보/20260811_리소스배포_랜딩.xlsx
+++ b/서버정보/20260811_리소스배포_랜딩.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37B2855E-A9FD-4D3C-B02E-5350AC9100C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5570C6C1-F654-480F-AE7A-A8E545E6B675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1658,7 +1658,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2118" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2117" uniqueCount="360">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3027,7 +3027,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>10.155.161.159</t>
+    <t>10.155.161.155</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6764,7 +6764,7 @@
         <v>352</v>
       </c>
       <c r="G16" s="69" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="H16" s="88" t="s">
         <v>329</v>
@@ -6851,7 +6851,7 @@
         <v>353</v>
       </c>
       <c r="G17" s="69" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H17" s="88" t="s">
         <v>329</v>
@@ -6862,9 +6862,7 @@
       <c r="J17" s="88">
         <v>8</v>
       </c>
-      <c r="K17" s="88" t="s">
-        <v>122</v>
-      </c>
+      <c r="K17" s="88"/>
       <c r="L17" s="96" t="s">
         <v>120</v>
       </c>
@@ -6938,7 +6936,7 @@
         <v>354</v>
       </c>
       <c r="G18" s="69" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H18" s="88" t="s">
         <v>329</v>
@@ -7025,7 +7023,7 @@
         <v>355</v>
       </c>
       <c r="G19" s="88" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H19" s="88" t="s">
         <v>329</v>
@@ -17890,9 +17888,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -18040,26 +18041,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -18083,9 +18073,17 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/서버정보/20260811_리소스배포_랜딩.xlsx
+++ b/서버정보/20260811_리소스배포_랜딩.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5570C6C1-F654-480F-AE7A-A8E545E6B675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F092BA98-13B6-4FA5-822B-0DB18FF2DD23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1658,7 +1658,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2117" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2118" uniqueCount="360">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -6862,7 +6862,9 @@
       <c r="J17" s="88">
         <v>8</v>
       </c>
-      <c r="K17" s="88"/>
+      <c r="K17" s="88" t="s">
+        <v>122</v>
+      </c>
       <c r="L17" s="96" t="s">
         <v>120</v>
       </c>
@@ -17888,12 +17890,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -18041,15 +18040,26 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -18073,17 +18083,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/서버정보/20260811_리소스배포_랜딩.xlsx
+++ b/서버정보/20260811_리소스배포_랜딩.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F092BA98-13B6-4FA5-822B-0DB18FF2DD23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76A8446D-9264-426E-A200-D6254457A1F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2987,10 +2987,6 @@
     <t>10.155.161.199</t>
   </si>
   <si>
-    <t>/subscriptions/b73b1d70-b43f-41b5-bb3f-34b9236d2ed9/resourceGroups/hazr-l-mgmt-rg/providers/Microsoft.Compute/galleries/hazrlmgmtgal/images/RHEL_9.8_Base_Image/versions/0.0.4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>l-ertest-sbn</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3028,6 +3024,10 @@
   </si>
   <si>
     <t>10.155.161.155</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/subscriptions/38befed7-7726-4784-910e-0cea5422077d/resourceGroups/hazr-d-dch-rg/providers/Microsoft.Compute/galleries/temp_ertest_gallery/images/temp_ertest_vm_image/versions/0.0.2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6437,7 +6437,7 @@
         <v>292</v>
       </c>
       <c r="N12" s="97" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="O12" s="98" t="str">
         <f t="shared" si="4"/>
@@ -6469,7 +6469,7 @@
         <v>138</v>
       </c>
       <c r="Z12" s="69" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AA12" s="88" t="b">
         <v>1</v>
@@ -6524,7 +6524,7 @@
         <v>292</v>
       </c>
       <c r="N13" s="97" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="O13" s="98" t="str">
         <f t="shared" si="4"/>
@@ -6556,7 +6556,7 @@
         <v>138</v>
       </c>
       <c r="Z13" s="88" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AA13" s="88" t="b">
         <v>1</v>
@@ -6611,7 +6611,7 @@
         <v>292</v>
       </c>
       <c r="N14" s="97" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="O14" s="98" t="str">
         <f t="shared" si="4"/>
@@ -6643,7 +6643,7 @@
         <v>138</v>
       </c>
       <c r="Z14" s="69" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AA14" s="88" t="b">
         <v>1</v>
@@ -6698,7 +6698,7 @@
         <v>292</v>
       </c>
       <c r="N15" s="97" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="O15" s="98" t="str">
         <f t="shared" si="4"/>
@@ -6730,7 +6730,7 @@
         <v>138</v>
       </c>
       <c r="Z15" s="88" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AA15" s="88" t="b">
         <v>1</v>
@@ -6761,10 +6761,10 @@
         <v>24</v>
       </c>
       <c r="F16" s="69" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G16" s="69" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H16" s="88" t="s">
         <v>329</v>
@@ -6785,7 +6785,7 @@
         <v>292</v>
       </c>
       <c r="N16" s="97" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="O16" s="106" t="str">
         <f t="shared" ref="O16:O19" si="6">SUBSTITUTE(F16,"hazr-","")&amp;"-osdisk"</f>
@@ -6848,10 +6848,10 @@
         <v>24</v>
       </c>
       <c r="F17" s="69" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="G17" s="69" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H17" s="88" t="s">
         <v>329</v>
@@ -6872,7 +6872,7 @@
         <v>292</v>
       </c>
       <c r="N17" s="97" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="O17" s="106" t="str">
         <f t="shared" si="6"/>
@@ -6935,10 +6935,10 @@
         <v>24</v>
       </c>
       <c r="F18" s="69" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="G18" s="69" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H18" s="88" t="s">
         <v>329</v>
@@ -6959,7 +6959,7 @@
         <v>292</v>
       </c>
       <c r="N18" s="97" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="O18" s="106" t="str">
         <f t="shared" si="6"/>
@@ -7022,10 +7022,10 @@
         <v>24</v>
       </c>
       <c r="F19" s="88" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G19" s="88" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H19" s="88" t="s">
         <v>329</v>
@@ -7046,7 +7046,7 @@
         <v>292</v>
       </c>
       <c r="N19" s="97" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="O19" s="98" t="str">
         <f t="shared" si="6"/>
@@ -9374,7 +9374,7 @@
         <v>321</v>
       </c>
       <c r="C12" s="73" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D12" s="73" t="s">
         <v>145</v>
@@ -9390,7 +9390,7 @@
         <v>138</v>
       </c>
       <c r="H12" s="73" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="I12" s="102" t="s">
         <v>341</v>
@@ -9412,7 +9412,7 @@
         <v>321</v>
       </c>
       <c r="C13" s="75" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D13" s="75" t="s">
         <v>145</v>
@@ -9428,7 +9428,7 @@
         <v>138</v>
       </c>
       <c r="H13" s="75" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="I13" s="101" t="s">
         <v>343</v>
@@ -9450,7 +9450,7 @@
         <v>321</v>
       </c>
       <c r="C14" s="73" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D14" s="73" t="s">
         <v>145</v>
@@ -9466,7 +9466,7 @@
         <v>138</v>
       </c>
       <c r="H14" s="73" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="I14" s="102" t="s">
         <v>342</v>
@@ -9488,7 +9488,7 @@
         <v>321</v>
       </c>
       <c r="C15" s="75" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D15" s="75" t="s">
         <v>145</v>
@@ -9504,7 +9504,7 @@
         <v>138</v>
       </c>
       <c r="H15" s="75" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="I15" s="101" t="s">
         <v>344</v>
@@ -9545,7 +9545,7 @@
         <v>290</v>
       </c>
       <c r="I16" s="68" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="J16" s="73" t="s">
         <v>145</v>
@@ -9583,7 +9583,7 @@
         <v>290</v>
       </c>
       <c r="I17" s="69" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="J17" s="75" t="s">
         <v>145</v>
@@ -9621,7 +9621,7 @@
         <v>290</v>
       </c>
       <c r="I18" s="68" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="J18" s="73" t="s">
         <v>145</v>
@@ -9659,7 +9659,7 @@
         <v>290</v>
       </c>
       <c r="I19" s="101" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="J19" s="75" t="s">
         <v>145</v>
@@ -17890,9 +17890,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -18040,26 +18043,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -18083,9 +18075,17 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/서버정보/20260811_리소스배포_랜딩.xlsx
+++ b/서버정보/20260811_리소스배포_랜딩.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76A8446D-9264-426E-A200-D6254457A1F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6620AC3E-4BD6-4C0B-AD9F-90F2DFDEDCAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1658,7 +1658,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2118" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2117" uniqueCount="360">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -6403,9 +6403,7 @@
       <c r="B12" s="88" t="s">
         <v>321</v>
       </c>
-      <c r="C12" s="88" t="s">
-        <v>340</v>
-      </c>
+      <c r="C12" s="88"/>
       <c r="D12" s="88" t="s">
         <v>145</v>
       </c>
@@ -17890,12 +17888,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -18043,15 +18038,26 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -18075,17 +18081,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/서버정보/20260811_리소스배포_랜딩.xlsx
+++ b/서버정보/20260811_리소스배포_랜딩.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6620AC3E-4BD6-4C0B-AD9F-90F2DFDEDCAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9864A9DF-5AE5-414A-BED1-C9FEFCFA3A03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3027,7 +3027,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>/subscriptions/38befed7-7726-4784-910e-0cea5422077d/resourceGroups/hazr-d-dch-rg/providers/Microsoft.Compute/galleries/temp_ertest_gallery/images/temp_ertest_vm_image/versions/0.0.2</t>
+    <t>/subscriptions/38befed7-7226-4784-910e-0cea5422077d/resourceGroups/hazr-d-dch-rg/providers/Microsoft.Compute/galleries/temp_ertest_gallery/images/temp_ertest_vm_image/versions/0.0.2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6434,7 +6434,7 @@
       <c r="M12" s="88" t="s">
         <v>292</v>
       </c>
-      <c r="N12" s="97" t="s">
+      <c r="N12" s="1" t="s">
         <v>359</v>
       </c>
       <c r="O12" s="98" t="str">
@@ -6521,7 +6521,7 @@
       <c r="M13" s="88" t="s">
         <v>292</v>
       </c>
-      <c r="N13" s="97" t="s">
+      <c r="N13" s="1" t="s">
         <v>359</v>
       </c>
       <c r="O13" s="98" t="str">
@@ -6608,7 +6608,7 @@
       <c r="M14" s="88" t="s">
         <v>292</v>
       </c>
-      <c r="N14" s="97" t="s">
+      <c r="N14" s="1" t="s">
         <v>359</v>
       </c>
       <c r="O14" s="98" t="str">
@@ -6695,7 +6695,7 @@
       <c r="M15" s="88" t="s">
         <v>292</v>
       </c>
-      <c r="N15" s="97" t="s">
+      <c r="N15" s="1" t="s">
         <v>359</v>
       </c>
       <c r="O15" s="98" t="str">
@@ -6782,7 +6782,7 @@
       <c r="M16" s="88" t="s">
         <v>292</v>
       </c>
-      <c r="N16" s="97" t="s">
+      <c r="N16" s="1" t="s">
         <v>359</v>
       </c>
       <c r="O16" s="106" t="str">
@@ -6869,7 +6869,7 @@
       <c r="M17" s="88" t="s">
         <v>292</v>
       </c>
-      <c r="N17" s="97" t="s">
+      <c r="N17" s="1" t="s">
         <v>359</v>
       </c>
       <c r="O17" s="106" t="str">
@@ -6956,7 +6956,7 @@
       <c r="M18" s="88" t="s">
         <v>292</v>
       </c>
-      <c r="N18" s="97" t="s">
+      <c r="N18" s="1" t="s">
         <v>359</v>
       </c>
       <c r="O18" s="106" t="str">
@@ -7043,7 +7043,7 @@
       <c r="M19" s="88" t="s">
         <v>292</v>
       </c>
-      <c r="N19" s="97" t="s">
+      <c r="N19" s="1" t="s">
         <v>359</v>
       </c>
       <c r="O19" s="98" t="str">
@@ -17888,9 +17888,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -18038,26 +18041,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -18081,9 +18073,17 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>